--- a/Decipher-PMO-Project-Workbook.xlsx
+++ b/Decipher-PMO-Project-Workbook.xlsx
@@ -9,23 +9,24 @@
   </bookViews>
   <sheets>
     <sheet name="How to Use" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Identification" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Charter" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RACI" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="WBS &amp; Estimates" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Schedule" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Budget &amp; EVM" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Time &amp; Cost" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Risk Register" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="RAID" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="RTM" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Dependencies" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Decisions &amp; Changes" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Change Requests" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="UAT Log" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="Escalation Log" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="Status" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="Lessons" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Glossary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Identification" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Charter" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RACI" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="WBS &amp; Estimates" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Schedule" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Budget &amp; EVM" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Time &amp; Cost" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Risk Register" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="RAID" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="RTM" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Dependencies" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Decisions &amp; Changes" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Change Requests" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="UAT Log" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Escalation Log" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Status" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Lessons" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="467">
   <si>
     <t xml:space="preserve">Decipher PMO — Project Workbook</t>
   </si>
@@ -147,6 +148,321 @@
     <t xml:space="preserve">Lessons learned register</t>
   </si>
   <si>
+    <t xml:space="preserve">Glossary — acronyms used in this workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every abbreviation used in the tabs, written out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acronym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project / Program Management Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PgM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Program Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Responsible Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business as Usual (steady-state operations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red / Amber / Green status rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risks, Assumptions, Issues, Dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsible, Accountable, Consulted, Informed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Control Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated Completion Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Performance Indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objectives and Key Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned Value Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost Variance (EV minus AC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Variance (EV minus PV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost Performance Index (EV divided by AC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Performance Index (EV divided by PV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget at Completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate at Completion (forecast final cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate to Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance at Completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Breakdown Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program Evaluation and Review Technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P x I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability x Impact (risk score)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirements Traceability Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Acceptance Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition of Ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition of Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement of Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request for Proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Level Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizational Change Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Time Equivalent (one full-time person)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Present Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Rate of Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return on Investment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governance, Risk, and Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity and Access Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZTNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Trust Network Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Privileged Access Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Information and Event Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Factor Authentication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IdP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtual Private Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCI-DSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Card Industry Data Security Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Organization for Standardization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Institute of Standards and Technology</t>
+  </si>
+  <si>
     <t xml:space="preserve">Project Identification</t>
   </si>
   <si>
@@ -168,9 +484,6 @@
     <t xml:space="preserve">CISO, Bristol Financial</t>
   </si>
   <si>
-    <t xml:space="preserve">TPM</t>
-  </si>
-  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
@@ -255,7 +568,7 @@
     <t xml:space="preserve">2026-01-10</t>
   </si>
   <si>
-    <t xml:space="preserve">RACI Matrix</t>
+    <t xml:space="preserve">RACI Matrix (Responsible, Accountable, Consulted, Informed)</t>
   </si>
   <si>
     <t xml:space="preserve">Use exactly one A per row.</t>
@@ -300,7 +613,7 @@
     <t xml:space="preserve">UAT sign-off</t>
   </si>
   <si>
-    <t xml:space="preserve">WBS &amp; Three-Point Estimates</t>
+    <t xml:space="preserve">Work Breakdown Structure (WBS) &amp; Three-Point Estimates</t>
   </si>
   <si>
     <t xml:space="preserve">PERT expected = (O + 4M + P)/6</t>
@@ -396,9 +709,6 @@
     <t xml:space="preserve">Variance (days)</t>
   </si>
   <si>
-    <t xml:space="preserve">RAG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Discovery complete</t>
   </si>
   <si>
@@ -435,10 +745,10 @@
     <t xml:space="preserve">2026-10-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget &amp; Earned Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPI=EV/AC, SPI=EV/PV, EAC=BAC/CPI. Blue = inputs.</t>
+    <t xml:space="preserve">Budget &amp; Earned Value (EVM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVM = Earned Value Management. CPI = Cost Performance Index (EV/AC); SPI = Schedule Performance Index (EV/PV); EAC = Estimate at Completion (BAC/CPI). Blue = inputs.</t>
   </si>
   <si>
     <t xml:space="preserve">BAC ($)</t>
@@ -456,18 +766,6 @@
     <t xml:space="preserve">Actual Cost (AC)</t>
   </si>
   <si>
-    <t xml:space="preserve">CV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wk 4</t>
   </si>
   <si>
@@ -579,7 +877,7 @@
     <t xml:space="preserve">Risk Register &amp; Response</t>
   </si>
   <si>
-    <t xml:space="preserve">Score = P x I (1-5 each). Residual after response.</t>
+    <t xml:space="preserve">Score = Probability x Impact (P x I, 1-5 each). Residual after response.</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -651,9 +949,6 @@
     <t xml:space="preserve">Sponsor ask for named testers</t>
   </si>
   <si>
-    <t xml:space="preserve">OCM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open</t>
   </si>
   <si>
@@ -672,7 +967,7 @@
     <t xml:space="preserve">Total residual exposure</t>
   </si>
   <si>
-    <t xml:space="preserve">RAID Log</t>
+    <t xml:space="preserve">RAID Log (Risks, Assumptions, Issues, Dependencies)</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
@@ -735,7 +1030,7 @@
     <t xml:space="preserve">Requirements Traceability</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage = % of requirements with a passing test.</t>
+    <t xml:space="preserve">Requirements Traceability Matrix (RTM). Coverage = % of requirements with a passing test.</t>
   </si>
   <si>
     <t xml:space="preserve">Req ID</t>
@@ -852,9 +1147,6 @@
     <t xml:space="preserve">Platform/IdP</t>
   </si>
   <si>
-    <t xml:space="preserve">ZTNA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAML federation</t>
   </si>
   <si>
@@ -879,9 +1171,6 @@
     <t xml:space="preserve">Vendor (BeyondTrust)</t>
   </si>
   <si>
-    <t xml:space="preserve">PAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vault deployment</t>
   </si>
   <si>
@@ -945,7 +1234,7 @@
     <t xml:space="preserve">Change Control (CCB)</t>
   </si>
   <si>
-    <t xml:space="preserve">Impact assessed before approval.</t>
+    <t xml:space="preserve">Formal change control. CCB = Change Control Board. Impact assessed before approval.</t>
   </si>
   <si>
     <t xml:space="preserve">CR ID</t>
@@ -999,7 +1288,7 @@
     <t xml:space="preserve">Approve</t>
   </si>
   <si>
-    <t xml:space="preserve">UAT Test Case Log</t>
+    <t xml:space="preserve">User Acceptance Testing (UAT) — Test Case Log</t>
   </si>
   <si>
     <t xml:space="preserve">Pass rate auto-calculated.</t>
@@ -1214,15 +1503,15 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1291,52 +1580,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1761,6 +2066,254 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <f aca="false">D5*E5</f>
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <f aca="false">I5*J5</f>
+        <v>8</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">D6*E6</f>
+        <v>15</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <f aca="false">I6*J6</f>
+        <v>6</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <f aca="false">D7*E7</f>
+        <v>9</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <f aca="false">I7*J7</f>
+        <v>4</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <f aca="false">D8*E8</f>
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <f aca="false">I8*J8</f>
+        <v>10</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <f aca="false">SUM(K5:K8)</f>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1775,27 +2328,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>213</v>
+        <v>311</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>214</v>
+        <v>312</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>32</v>
@@ -1803,71 +2356,71 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>217</v>
+        <v>315</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>218</v>
+        <v>316</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>205</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>220</v>
+        <v>318</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>221</v>
+        <v>319</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>223</v>
+        <v>321</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>224</v>
+        <v>322</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>205</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>226</v>
+        <v>324</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>227</v>
+        <v>325</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>228</v>
+        <v>326</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>230</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -1881,7 +2434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1900,123 +2453,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>231</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>233</v>
+        <v>331</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>237</v>
+        <v>335</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>239</v>
+        <v>337</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>240</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>241</v>
+        <v>339</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>242</v>
+        <v>340</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>244</v>
+        <v>342</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>246</v>
+        <v>344</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>248</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>249</v>
+        <v>347</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>250</v>
+        <v>348</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>251</v>
+        <v>349</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>252</v>
+        <v>350</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>253</v>
+        <v>351</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>254</v>
+        <v>352</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>256</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>258</v>
+        <v>356</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>259</v>
+        <v>357</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>260</v>
+        <v>358</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>261</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="B9" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIF(G5:G7,"Pass")/COUNTA(A5:A7),0)</f>
         <v>0.333333333333333</v>
       </c>
@@ -2032,7 +2585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2050,50 +2603,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>263</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>266</v>
+        <v>364</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>269</v>
+        <v>367</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>270</v>
+        <v>368</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>-3</v>
@@ -2101,22 +2654,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>273</v>
+        <v>370</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>274</v>
+        <v>371</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>6</v>
@@ -2124,22 +2677,22 @@
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>281</v>
+        <v>377</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>282</v>
+        <v>378</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>4</v>
@@ -2156,7 +2709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2174,27 +2727,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>283</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>284</v>
+        <v>380</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>285</v>
+        <v>381</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>286</v>
+        <v>382</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>287</v>
+        <v>383</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>32</v>
@@ -2202,48 +2755,48 @@
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>289</v>
+        <v>385</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>290</v>
+        <v>386</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>291</v>
+        <v>387</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>292</v>
+        <v>388</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>293</v>
+        <v>389</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>294</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>295</v>
+        <v>391</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>296</v>
+        <v>392</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>297</v>
+        <v>393</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>298</v>
+        <v>394</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2257,7 +2810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2277,49 +2830,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>301</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>302</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>303</v>
+        <v>399</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>304</v>
+        <v>400</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>305</v>
+        <v>401</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>307</v>
+        <v>403</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>308</v>
+        <v>404</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>309</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>310</v>
+        <v>406</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>312</v>
+        <v>408</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>5</v>
@@ -2328,24 +2881,24 @@
         <v>18000</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>313</v>
+        <v>409</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>314</v>
+        <v>410</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>260</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>315</v>
+        <v>411</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>316</v>
+        <v>412</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>317</v>
+        <v>413</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>3</v>
@@ -2354,13 +2907,13 @@
         <v>22000</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>318</v>
+        <v>414</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>319</v>
+        <v>415</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +2927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2391,98 +2944,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>320</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>322</v>
+        <v>418</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>323</v>
+        <v>419</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>324</v>
+        <v>420</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>239</v>
+        <v>337</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>325</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>246</v>
+        <v>344</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>326</v>
+        <v>422</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>327</v>
+        <v>423</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>328</v>
+        <v>424</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>329</v>
+        <v>425</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>330</v>
+        <v>426</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>254</v>
+        <v>352</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>332</v>
+        <v>428</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>333</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>334</v>
+        <v>430</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>335</v>
+        <v>431</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>330</v>
+        <v>426</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="E8" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D10" s="11" t="n">
+      <c r="B10" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="D10" s="15" t="n">
         <f aca="false">IFERROR(COUNTIF(D5:D8,"Pass")/COUNTA(D5:D8),0)</f>
         <v>0.75</v>
       </c>
@@ -2498,7 +3051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2523,54 +3076,54 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>337</v>
+        <v>433</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>220</v>
+        <v>318</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>338</v>
+        <v>434</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>339</v>
+        <v>435</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>340</v>
+        <v>436</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>341</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>342</v>
+        <v>438</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>343</v>
+        <v>439</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>344</v>
+        <v>440</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>345</v>
+        <v>441</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>48</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>346</v>
+        <v>442</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>347</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -2584,7 +3137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2603,58 +3156,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>350</v>
+        <v>446</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>351</v>
+        <v>447</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>352</v>
+        <v>448</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>353</v>
+        <v>449</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>354</v>
+        <v>450</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>355</v>
+        <v>451</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>356</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>145</v>
+        <v>244</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>357</v>
+        <v>453</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>358</v>
+        <v>454</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -2668,7 +3221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2685,24 +3238,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>359</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>360</v>
+        <v>456</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>361</v>
+        <v>457</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>308</v>
+        <v>404</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
@@ -2710,42 +3263,42 @@
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>362</v>
+        <v>458</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>363</v>
+        <v>459</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>364</v>
+        <v>460</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>365</v>
+        <v>461</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>205</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>366</v>
+        <v>462</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>367</v>
+        <v>463</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>369</v>
+        <v>465</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>223</v>
+        <v>321</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>370</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -2764,88 +3317,445 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="6" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="6" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2864,80 +3774,88 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>144</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>61</v>
+        <v>146</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>46</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>149</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>151</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>69</v>
+        <v>153</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>71</v>
+        <v>155</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2956,6 +3874,98 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2968,55 +3978,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="G5" s="5" t="str">
         <f aca="false">IF(COUNTIF(B5:F5,"A")=1,"OK","FIX")</f>
@@ -3025,22 +4035,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="G6" s="5" t="str">
         <f aca="false">IF(COUNTIF(B6:F6,"A")=1,"OK","FIX")</f>
@@ -3049,22 +4059,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="G7" s="5" t="str">
         <f aca="false">IF(COUNTIF(B7:F7,"A")=1,"OK","FIX")</f>
@@ -3073,22 +4083,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="G8" s="5" t="str">
         <f aca="false">IF(COUNTIF(B8:F8,"A")=1,"OK","FIX")</f>
@@ -3097,22 +4107,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="str">
         <f aca="false">IF(COUNTIF(B9:F9,"A")=1,"OK","FIX")</f>
@@ -3130,7 +4140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3150,49 +4160,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>92</v>
+        <v>196</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>97</v>
+        <v>201</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>8</v>
@@ -3214,13 +4224,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>10</v>
@@ -3242,13 +4252,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>18</v>
@@ -3270,13 +4280,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>6</v>
@@ -3298,13 +4308,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>6</v>
@@ -3326,13 +4336,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -3353,167 +4363,12 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="B11" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="11" t="n">
         <f aca="false">SUM(G5:G10)</f>
         <v>103.666666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <f aca="false">C5-B5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="8" t="str">
-        <f aca="false">IF(D5&lt;=5,"Green",IF(D5&lt;=14,"Amber","Red"))</f>
-        <v>Green</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <f aca="false">C6-B6</f>
-        <v>7</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="8" t="str">
-        <f aca="false">IF(D6&lt;=5,"Green",IF(D6&lt;=14,"Amber","Red"))</f>
-        <v>Amber</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <f aca="false">C7-B7</f>
-        <v>14</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8" t="str">
-        <f aca="false">IF(D7&lt;=5,"Green",IF(D7&lt;=14,"Amber","Red"))</f>
-        <v>Amber</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <f aca="false">C8-B8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="8" t="str">
-        <f aca="false">IF(D8&lt;=5,"Green",IF(D8&lt;=14,"Amber","Red"))</f>
-        <v>Green</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">C9-B9</f>
-        <v>9</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="8" t="str">
-        <f aca="false">IF(D9&lt;=5,"Green",IF(D9&lt;=14,"Amber","Red"))</f>
-        <v>Amber</v>
       </c>
     </row>
   </sheetData>
@@ -3532,165 +4387,143 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>132</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>142</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <f aca="false">C5-B5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="12" t="str">
+        <f aca="false">IF(D5&lt;=5,"Green",IF(D5&lt;=14,"Amber","Red"))</f>
+        <v>Green</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <f aca="false">C6-B6</f>
+        <v>7</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="12" t="str">
+        <f aca="false">IF(D6&lt;=5,"Green",IF(D6&lt;=14,"Amber","Red"))</f>
+        <v>Amber</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>290000</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>310000</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <f aca="false">C7-D7</f>
-        <v>-20000</v>
-      </c>
-      <c r="F7" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <f aca="false">C7-B7</f>
-        <v>-10000</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">IFERROR(C7/D7,0)</f>
-        <v>0.935483870967742</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <f aca="false">IFERROR(C7/B7,0)</f>
-        <v>0.966666666666667</v>
+        <v>14</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="12" t="str">
+        <f aca="false">IF(D7&lt;=5,"Green",IF(D7&lt;=14,"Amber","Red"))</f>
+        <v>Amber</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>650000</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <f aca="false">C8-D8</f>
-        <v>-50000</v>
-      </c>
-      <c r="F8" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <f aca="false">C8-B8</f>
-        <v>-40000</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <f aca="false">IFERROR(C8/D8,0)</f>
-        <v>0.923076923076923</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.9375</v>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="12" t="str">
+        <f aca="false">IF(D8&lt;=5,"Green",IF(D8&lt;=14,"Amber","Red"))</f>
+        <v>Green</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1080000</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <f aca="false">C9-D9</f>
-        <v>-130000</v>
-      </c>
-      <c r="F9" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <f aca="false">C9-B9</f>
-        <v>-150000</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">IFERROR(C9/D9,0)</f>
-        <v>0.87962962962963</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0.863636363636364</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <f aca="false">IFERROR($B$4/G9,0)</f>
-        <v>2728421.05263158</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <f aca="false">$B$4-B11</f>
-        <v>-328421.052631579</v>
+        <v>9</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="12" t="str">
+        <f aca="false">IF(D9&lt;=5,"Green",IF(D9&lt;=14,"Amber","Red"))</f>
+        <v>Amber</v>
       </c>
     </row>
   </sheetData>
@@ -3705,6 +4538,183 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>310000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <f aca="false">C7-D7</f>
+        <v>-20000</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <f aca="false">C7-B7</f>
+        <v>-10000</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <f aca="false">IFERROR(C7/D7,0)</f>
+        <v>0.935483870967742</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <f aca="false">IFERROR(C7/B7,0)</f>
+        <v>0.966666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>640000</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>650000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <f aca="false">C8-D8</f>
+        <v>-50000</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <f aca="false">C8-B8</f>
+        <v>-40000</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <f aca="false">IFERROR(C8/D8,0)</f>
+        <v>0.923076923076923</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <f aca="false">IFERROR(C8/B8,0)</f>
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>950000</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <f aca="false">C9-D9</f>
+        <v>-130000</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <f aca="false">C9-B9</f>
+        <v>-150000</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <f aca="false">IFERROR(C9/D9,0)</f>
+        <v>0.87962962962963</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <f aca="false">IFERROR(C9/B9,0)</f>
+        <v>0.863636363636364</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <f aca="false">IFERROR($B$4/G9,0)</f>
+        <v>2728421.05263158</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <f aca="false">$B$4-B11</f>
+        <v>-328421.052631579</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3725,482 +4735,234 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>155</v>
+        <v>254</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="10" t="n">
         <v>32</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">D5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="10" t="n">
         <v>210</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="10" t="n">
         <v>520</v>
       </c>
       <c r="I5" s="5" t="n">
         <f aca="false">D5*H5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="14" t="n">
         <f aca="false">IFERROR((D5*G5)/I5,0)</f>
         <v>0</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="10" t="n">
         <v>30</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="10" t="n">
         <v>520</v>
       </c>
       <c r="I6" s="5" t="n">
         <f aca="false">D6*H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="J6" s="14" t="n">
         <f aca="false">IFERROR((D6*G6)/I6,0)</f>
         <v>0</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>168</v>
+        <v>267</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>268</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>145</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="10" t="n">
         <v>38</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
         <v>5510</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="10" t="n">
         <v>360</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="10" t="n">
         <v>640</v>
       </c>
       <c r="I7" s="5" t="n">
         <f aca="false">D7*H7</f>
         <v>92800</v>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="J7" s="14" t="n">
         <f aca="false">IFERROR((D7*G7)/I7,0)</f>
         <v>0.5625</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>169</v>
+        <v>268</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="6" t="n">
+        <v>273</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="10" t="n">
         <v>12</v>
       </c>
       <c r="F8" s="5" t="n">
         <f aca="false">D8*E8</f>
         <v>1920</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="10" t="n">
         <v>160</v>
       </c>
       <c r="I8" s="5" t="n">
         <f aca="false">D8*H8</f>
         <v>25600</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" s="14" t="n">
         <f aca="false">IFERROR((D8*G8)/I8,0)</f>
         <v>0.075</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9" s="7" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>7430</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="11" t="n">
         <f aca="false">SUM(I5:I8)</f>
         <v>118400</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <f aca="false">D5*E5</f>
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <f aca="false">I5*J5</f>
-        <v>8</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <f aca="false">D6*E6</f>
-        <v>15</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <f aca="false">I6*J6</f>
-        <v>6</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <f aca="false">D7*E7</f>
-        <v>9</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <f aca="false">I7*J7</f>
-        <v>4</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <f aca="false">D8*E8</f>
-        <v>10</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <f aca="false">I8*J8</f>
-        <v>10</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <f aca="false">SUM(K5:K8)</f>
-        <v>28</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/Decipher-PMO-Project-Workbook.xlsx
+++ b/Decipher-PMO-Project-Workbook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="465">
   <si>
     <t xml:space="preserve">Decipher PMO — Project Workbook</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Identification</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name, sponsor, TPM, dates, current RAG</t>
+    <t xml:space="preserve">Project name, sponsor, PM, dates, current RAG</t>
   </si>
   <si>
     <t xml:space="preserve">Charter</t>
@@ -176,12 +176,6 @@
   </si>
   <si>
     <t xml:space="preserve">Program Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Program Manager</t>
   </si>
   <si>
     <t xml:space="preserve">SRO</t>
@@ -1580,7 +1574,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1603,14 +1597,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1725,34 +1711,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1898,7 +1884,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="80"/>
@@ -2067,7 +2053,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -2083,47 +2069,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>32</v>
@@ -2131,13 +2117,13 @@
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>4</v>
@@ -2150,10 +2136,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>2</v>
@@ -2166,18 +2152,18 @@
         <v>8</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>3</v>
@@ -2190,10 +2176,10 @@
         <v>15</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>2</v>
@@ -2206,18 +2192,18 @@
         <v>6</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3</v>
@@ -2230,10 +2216,10 @@
         <v>9</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>2</v>
@@ -2246,15 +2232,15 @@
         <v>4</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>12</v>
@@ -2270,10 +2256,10 @@
         <v>10</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>5</v>
@@ -2286,14 +2272,14 @@
         <v>10</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="K10" s="11" t="n">
+      <c r="B10" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="K10" s="9" t="n">
         <f aca="false">SUM(K5:K8)</f>
         <v>28</v>
       </c>
@@ -2315,7 +2301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -2328,27 +2314,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>32</v>
@@ -2356,71 +2342,71 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>316</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -2440,7 +2426,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -2453,123 +2439,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G7" s="5" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">IFERROR(COUNTIF(G5:G7,"Pass")/COUNTA(A5:A7),0)</f>
         <v>0.333333333333333</v>
       </c>
@@ -2591,7 +2577,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -2603,50 +2589,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>369</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>-3</v>
@@ -2654,22 +2640,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>374</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>6</v>
@@ -2677,22 +2663,22 @@
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>378</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>4</v>
@@ -2715,7 +2701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
@@ -2727,27 +2713,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>32</v>
@@ -2755,48 +2741,48 @@
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>388</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>394</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2816,7 +2802,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -2830,49 +2816,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>408</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>5</v>
@@ -2881,24 +2867,24 @@
         <v>18000</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>413</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>3</v>
@@ -2907,13 +2893,13 @@
         <v>22000</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +2919,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
@@ -2944,98 +2930,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>427</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="13" t="n">
         <f aca="false">IFERROR(COUNTIF(D5:D8,"Pass")/COUNTA(D5:D8),0)</f>
         <v>0.75</v>
       </c>
@@ -3057,7 +3043,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -3076,54 +3062,54 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>441</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>48</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -3143,7 +3129,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
@@ -3156,58 +3142,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -3227,7 +3213,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -3238,24 +3224,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
@@ -3263,42 +3249,42 @@
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>461</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>464</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -3318,444 +3304,444 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B56"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="5" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="5" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="B35" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B55" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3775,7 +3761,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
@@ -3783,79 +3769,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>148</v>
+        <v>42</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3875,7 +3861,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
@@ -3883,71 +3869,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3967,7 +3953,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
@@ -3978,55 +3964,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G5" s="5" t="str">
         <f aca="false">IF(COUNTIF(B5:F5,"A")=1,"OK","FIX")</f>
@@ -4035,22 +4021,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G6" s="5" t="str">
         <f aca="false">IF(COUNTIF(B6:F6,"A")=1,"OK","FIX")</f>
@@ -4059,22 +4045,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G7" s="5" t="str">
         <f aca="false">IF(COUNTIF(B7:F7,"A")=1,"OK","FIX")</f>
@@ -4083,22 +4069,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G8" s="5" t="str">
         <f aca="false">IF(COUNTIF(B8:F8,"A")=1,"OK","FIX")</f>
@@ -4107,22 +4093,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="5" t="str">
         <f aca="false">IF(COUNTIF(B9:F9,"A")=1,"OK","FIX")</f>
@@ -4146,7 +4132,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -4160,49 +4146,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>8</v>
@@ -4224,13 +4210,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>10</v>
@@ -4252,13 +4238,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>18</v>
@@ -4280,13 +4266,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>6</v>
@@ -4308,13 +4294,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>6</v>
@@ -4336,13 +4322,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -4363,10 +4349,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="B11" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="9" t="n">
         <f aca="false">SUM(G5:G10)</f>
         <v>103.666666666667</v>
       </c>
@@ -4388,7 +4374,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="15"/>
@@ -4398,130 +4384,130 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">C5-B5</f>
         <v>0</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="12" t="str">
+      <c r="F5" s="10" t="str">
         <f aca="false">IF(D5&lt;=5,"Green",IF(D5&lt;=14,"Amber","Red"))</f>
         <v>Green</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">C6-B6</f>
         <v>7</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="12" t="str">
+      <c r="F6" s="10" t="str">
         <f aca="false">IF(D6&lt;=5,"Green",IF(D6&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">C7-B7</f>
         <v>14</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="12" t="str">
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(D7&lt;=5,"Green",IF(D7&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">C8-B8</f>
         <v>0</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="12" t="str">
+      <c r="F8" s="10" t="str">
         <f aca="false">IF(D8&lt;=5,"Green",IF(D8&lt;=14,"Amber","Red"))</f>
         <v>Green</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">C9-B9</f>
         <v>9</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="12" t="str">
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(D9&lt;=5,"Green",IF(D9&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
@@ -4543,7 +4529,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
@@ -4553,59 +4539,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" s="13" t="n">
+      <c r="A4" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="11" t="n">
         <v>2400000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="E6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="B7" s="8" t="n">
         <v>300000</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="8" t="n">
         <v>290000</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="8" t="n">
         <v>310000</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -4627,15 +4613,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B8" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="B8" s="8" t="n">
         <v>640000</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="8" t="n">
         <v>600000</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="8" t="n">
         <v>650000</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -4657,15 +4643,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="10" t="n">
+        <v>242</v>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>1100000</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="8" t="n">
         <v>950000</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="8" t="n">
         <v>1080000</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -4686,19 +4672,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="11" t="n">
+      <c r="A11" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <f aca="false">IFERROR($B$4/G9,0)</f>
         <v>2728421.05263158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="11" t="n">
+      <c r="A12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <f aca="false">$B$4-B11</f>
         <v>-328421.052631579</v>
       </c>
@@ -4720,7 +4706,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -4737,47 +4723,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>32</v>
@@ -4785,184 +4771,184 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="8" t="n">
         <v>32</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">D5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="8" t="n">
         <v>210</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="8" t="n">
         <v>520</v>
       </c>
       <c r="I5" s="5" t="n">
         <f aca="false">D5*H5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="12" t="n">
         <f aca="false">IFERROR((D5*G5)/I5,0)</f>
         <v>0</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>264</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="8" t="n">
         <v>30</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="8" t="n">
         <v>520</v>
       </c>
       <c r="I6" s="5" t="n">
         <f aca="false">D6*H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="12" t="n">
         <f aca="false">IFERROR((D6*G6)/I6,0)</f>
         <v>0</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="8" t="n">
         <v>38</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
         <v>5510</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="8" t="n">
         <v>640</v>
       </c>
       <c r="I7" s="5" t="n">
         <f aca="false">D7*H7</f>
         <v>92800</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="12" t="n">
         <f aca="false">IFERROR((D7*G7)/I7,0)</f>
         <v>0.5625</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>271</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>160</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="F8" s="5" t="n">
         <f aca="false">D8*E8</f>
         <v>1920</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="8" t="n">
         <v>160</v>
       </c>
       <c r="I8" s="5" t="n">
         <f aca="false">D8*H8</f>
         <v>25600</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="12" t="n">
         <f aca="false">IFERROR((D8*G8)/I8,0)</f>
         <v>0.075</v>
       </c>
       <c r="K8" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="9" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>7430</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="9" t="n">
         <f aca="false">SUM(I5:I8)</f>
         <v>118400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
